--- a/.agents/governance/primecare_governance_audit.xlsx
+++ b/.agents/governance/primecare_governance_audit.xlsx
@@ -783,7 +783,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -884,4198 +884,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>missing_widget</t>
+          <t>info</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_regional_manager_usa_dashboard_controller_audit_logs') in dashboard 'RegionalManagerUsaDashboardController' is missing in the code.</t>
+          <t>Relational database initialized and dynamically seeded successfully.</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>115</v>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'RegionalManagerUsaDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_scrum_master_dashboard_controller_audit_logs') in dashboard 'ScrumMasterDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'ScrumMasterDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_territory_expansion_manager_dashboard_controller_audit_logs') in dashboard 'TerritoryExpansionManagerDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'TerritoryExpansionManagerDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_territory_sales_manager_dashboard_controller_audit_logs') in dashboard 'TerritorySalesManagerDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'TerritorySalesManagerDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>122</v>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_psw_dashboard_controller_audit_logs') in dashboard 'PswDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'PswDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>124</v>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_rn_dashboard_controller_audit_logs') in dashboard 'RnDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'RnDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>126</v>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_rpn_dashboard_controller_audit_logs') in dashboard 'RpnDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'RpnDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'BillingAdminDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'HrHiringDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_hr_hiring_dashboard_controller_audit_logs') in dashboard 'HrHiringDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>131</v>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'HrHiringDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'HrManagerDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>133</v>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_hr_manager_dashboard_controller_audit_logs') in dashboard 'HrManagerDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4" t="n">
-        <v>134</v>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'HrManagerDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>135</v>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'IntakeCoordinatorDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="4" t="n">
-        <v>136</v>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_intake_coordinator_dashboard_controller_audit_logs') in dashboard 'IntakeCoordinatorDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>137</v>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'IntakeCoordinatorDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>138</v>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'QualityAssuranceDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>139</v>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_quality_assurance_dashboard_controller_audit_logs') in dashboard 'QualityAssuranceDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'QualityAssuranceDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>141</v>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'ReceptionistDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="4" t="n">
-        <v>142</v>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_receptionist_dashboard_controller_audit_logs') in dashboard 'ReceptionistDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="5" t="n">
-        <v>143</v>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'ReceptionistDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="4" t="n">
-        <v>144</v>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'SchedulerDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>145</v>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'TrainingCoordinatorDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>146</v>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_training_coordinator_dashboard_controller_audit_logs') in dashboard 'TrainingCoordinatorDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>147</v>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'TrainingCoordinatorDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>148</v>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'VolunteerCoordinatorDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>149</v>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_volunteer_coordinator_dashboard_controller_audit_logs') in dashboard 'VolunteerCoordinatorDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>150</v>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'VolunteerCoordinatorDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'SocialWorkerDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'SupportDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_support_dashboard_controller_audit_logs') in dashboard 'SupportDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'SupportDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'SystemDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="4" t="n">
-        <v>64</v>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_system_dashboard_controller_audit_logs') in dashboard 'SystemDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'SystemDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'SystemVerificationDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_system_verification_dashboard_controller_audit_logs') in dashboard 'SystemVerificationDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'SystemVerificationDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'TrainingHubDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_training_hub_dashboard_controller_audit_logs') in dashboard 'TrainingHubDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'TrainingHubDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_cfo_dashboard_controller_audit_logs') in dashboard 'CfoDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'CfoDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="4" t="n">
-        <v>74</v>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_coo_dashboard_notifier_audit_logs') in dashboard 'CooDashboardNotifier' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'CooDashboardNotifier' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_cto_dashboard_controller_audit_logs') in dashboard 'CtoDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'CtoDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="4" t="n">
-        <v>78</v>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_cx_director_dashboard_controller_audit_logs') in dashboard 'CxDirectorDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="5" t="n">
-        <v>79</v>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'CxDirectorDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="4" t="n">
-        <v>80</v>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_finance_director_dashboard_controller_audit_logs') in dashboard 'FinanceDirectorDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'FinanceDirectorDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="4" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_hr_director_dashboard_controller_audit_logs') in dashboard 'HrDirectorDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'HrDirectorDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="4" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_legal_dashboard_controller_audit_logs') in dashboard 'LegalDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'LegalDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_owner_dashboard_controller_audit_logs') in dashboard 'OwnerDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'OwnerDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="4" t="n">
-        <v>88</v>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_shareholder_dashboard_controller_audit_logs') in dashboard 'ShareholderDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="5" t="n">
-        <v>89</v>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'ShareholderDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_training_director_dashboard_controller_audit_logs') in dashboard 'TrainingDirectorDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'TrainingDirectorDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_community_outreach_dashboard_controller_audit_logs') in dashboard 'CommunityOutreachDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'CommunityOutreachDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="4" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="C74" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_compliance_manager_dashboard_controller_audit_logs') in dashboard 'ComplianceManagerDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'ComplianceManagerDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="4" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_franchise_sales_manager_dashboard_controller_audit_logs') in dashboard 'FranchiseSalesManagerDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>97</v>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'FranchiseSalesManagerDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="4" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_general_manager_dashboard_controller_audit_logs') in dashboard 'GeneralManagerDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'GeneralManagerDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="4" t="n">
-        <v>100</v>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_governance_officer_dashboard_controller_audit_logs') in dashboard 'GovernanceOfficerDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'GovernanceOfficerDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="4" t="n">
-        <v>102</v>
-      </c>
-      <c r="C82" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_head_of_bus_dev_dashboard_controller_audit_logs') in dashboard 'HeadOfBusDevDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="5" t="n">
-        <v>103</v>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'HeadOfBusDevDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="4" t="n">
-        <v>104</v>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_head_of_marketing_dashboard_controller_audit_logs') in dashboard 'HeadOfMarketingDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="5" t="n">
-        <v>105</v>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'HeadOfMarketingDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E85" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="4" t="n">
-        <v>106</v>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_local_marketing_manager_dashboard_controller_audit_logs') in dashboard 'LocalMarketingManagerDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="5" t="n">
-        <v>107</v>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'LocalMarketingManagerDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="4" t="n">
-        <v>108</v>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_operations_manager_dashboard_controller_audit_logs') in dashboard 'OperationsManagerDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="5" t="n">
-        <v>109</v>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'OperationsManagerDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="4" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="C90" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_partnership_manager_dashboard_controller_audit_logs') in dashboard 'PartnershipManagerDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'PartnershipManagerDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_regional_bdm_dashboard_controller_audit_logs') in dashboard 'RegionalBdmDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="5" t="n">
-        <v>113</v>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'RegionalBdmDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:43</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_rmt_dashboard_controller_audit_logs') in dashboard 'RmtDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'RmtDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C96" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_clinical_dashboard_controller_audit_logs') in dashboard 'ClinicalDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="5" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'ClinicalDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'ArchitecturePlanningDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="5" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_architecture_planning_dashboard_controller_audit_logs') in dashboard 'ArchitecturePlanningDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'ArchitecturePlanningDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'BusinessDevelopmentDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_business_development_dashboard_controller_audit_logs') in dashboard 'BusinessDevelopmentDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C103" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'BusinessDevelopmentDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="4" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'ChiropractorDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C105" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_chiropractor_dashboard_controller_audit_logs') in dashboard 'ChiropractorDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="4" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C106" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'ChiropractorDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C107" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'ClinicDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="4" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_clinic_dashboard_controller_audit_logs') in dashboard 'ClinicDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="5" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="C109" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'ClinicDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E109" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="4" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'CourseArchitectDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="C111" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_course_architect_dashboard_controller_audit_logs') in dashboard 'CourseArchitectDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'CourseArchitectDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="5" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="C113" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'CustomerSupportDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_customer_support_dashboard_controller_audit_logs') in dashboard 'CustomerSupportDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="5" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'CustomerSupportDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'DynamicScreenDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="5" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_dynamic_dashboard_controller_audit_logs') in dashboard 'DynamicScreenDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'DynamicScreenDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'FamilyMemberDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F119" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_family_member_dashboard_controller_audit_logs') in dashboard 'FamilyMemberDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'FamilyMemberDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F121" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="4" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'FranchiseDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_franchise_dashboard_controller_audit_logs') in dashboard 'FranchiseDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F123" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="4" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'FranchiseDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'GuestDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F125" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_guest_dashboard_controller_audit_logs') in dashboard 'GuestDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'GuestDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F127" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="4" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'InfrastructureDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="5" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_infrastructure_dashboard_controller_audit_logs') in dashboard 'InfrastructureDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F129" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'InfrastructureDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F130" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="C131" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'IntakeDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E131" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F131" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_intake_dashboard_controller_audit_logs') in dashboard 'IntakeDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="C133" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'IntakeDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E133" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="4" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'OfficeDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F134" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="5" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="C135" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_office_dashboard_controller_audit_logs') in dashboard 'OfficeDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E135" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F135" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="4" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'OfficeDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F136" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="5" t="n">
-        <v>136</v>
-      </c>
-      <c r="B137" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="C137" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'PatientDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E137" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F137" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="4" t="n">
-        <v>137</v>
-      </c>
-      <c r="B138" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_patient_dashboard_controller_audit_logs') in dashboard 'PatientDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="5" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="C139" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'PatientDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="4" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'PhysiotherapistDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="20" customHeight="1">
-      <c r="A141" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="C141" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_physiotherapist_dashboard_controller_audit_logs') in dashboard 'PhysiotherapistDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E141" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F141" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="20" customHeight="1">
-      <c r="A142" s="4" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'PhysiotherapistDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'PortalDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F143" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="20" customHeight="1">
-      <c r="A144" s="4" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" s="4" t="n">
-        <v>52</v>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_portal_dashboard_controller_audit_logs') in dashboard 'PortalDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F144" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="20" customHeight="1">
-      <c r="A145" s="5" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="C145" s="5" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'PortalDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="20" customHeight="1">
-      <c r="A146" s="4" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" s="4" t="n">
-        <v>54</v>
-      </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'QaDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="20" customHeight="1">
-      <c r="A147" s="5" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_qa_dashboard_controller_audit_logs') in dashboard 'QaDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="4" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" s="4" t="n">
-        <v>56</v>
-      </c>
-      <c r="C148" s="4" t="inlineStr">
-        <is>
-          <t>undocumented_widget</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Undocumented Widget: Sidebar item 'Live Auditing timeline Console' (ID: 'audit_logs_terminal') in screen 'QaDashboardController' exists in code but is not declared in the database spec.</t>
-        </is>
-      </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F148" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="20" customHeight="1">
-      <c r="A149" s="5" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>layout_mismatch</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>Layout Mismatch: Dashboard 'SocialWorkerDashboardController' is 'Split Dual-Panel' in code, but database expects 'Single-Column'</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F149" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="20" customHeight="1">
-      <c r="A150" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" s="4" t="n">
-        <v>58</v>
-      </c>
-      <c r="C150" s="4" t="inlineStr">
-        <is>
-          <t>missing_widget</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Missing Widget Action: Expected action handler 'renderLogs' (Code: 'FUN_social_worker_dashboard_controller_audit_logs') in dashboard 'SocialWorkerDashboardController' is missing in the code.</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="F150" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="20" customHeight="1">
-      <c r="A151" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C151" s="5" t="inlineStr">
-        <is>
-          <t>info</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>Relational database initialized and dynamically seeded successfully.</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="F151" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
@@ -5192,7 +1020,7 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
@@ -5237,7 +1065,7 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
@@ -5282,7 +1110,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
@@ -5327,7 +1155,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
@@ -7955,7 +3783,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -7995,7 +3823,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -8035,7 +3863,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -8115,7 +3943,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -8195,7 +4023,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -8395,7 +4223,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -8475,7 +4303,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -8555,7 +4383,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -8595,7 +4423,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -8675,7 +4503,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -8835,7 +4663,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -8995,7 +4823,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -9035,7 +4863,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -9075,7 +4903,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -9115,7 +4943,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -9155,7 +4983,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -9275,7 +5103,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -9435,7 +5263,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -9475,7 +5303,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -9515,7 +5343,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -9595,7 +5423,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -9635,7 +5463,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -9675,7 +5503,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -9915,7 +5743,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -10035,7 +5863,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -10075,7 +5903,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
@@ -10115,7 +5943,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -10155,7 +5983,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
@@ -10275,7 +6103,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -10355,7 +6183,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -10395,7 +6223,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>masterLayout</t>
+          <t>adminLayout</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -10577,7 +6405,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -10618,7 +6446,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -10659,7 +6487,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -10700,7 +6528,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -10741,7 +6569,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -10782,7 +6610,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
@@ -10823,7 +6651,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -10864,7 +6692,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
@@ -10905,7 +6733,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -10946,7 +6774,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
@@ -10987,7 +6815,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -11028,7 +6856,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
@@ -11069,7 +6897,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -11110,7 +6938,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
@@ -11151,7 +6979,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -11192,7 +7020,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
@@ -11233,7 +7061,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -11274,7 +7102,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
@@ -11315,7 +7143,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
@@ -11356,7 +7184,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -11397,7 +7225,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -11438,7 +7266,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
@@ -12668,7 +8496,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
@@ -12709,7 +8537,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
@@ -12750,7 +8578,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
@@ -12791,7 +8619,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
@@ -12832,7 +8660,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -12873,7 +8701,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
@@ -12914,7 +8742,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -12955,7 +8783,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
@@ -12996,7 +8824,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
@@ -25097,7 +20925,7 @@
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -25441,7 +21269,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>CMP_architecture_planning_dashboard_controller_audit_logs</t>
+          <t>CMP_architecture_planning_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -25456,7 +21284,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
@@ -25464,7 +21292,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>FUN_architecture_planning_dashboard_controller_audit_logs</t>
+          <t>FUN_architecture_planning_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -25819,7 +21647,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>CMP_business_development_dashboard_controller_audit_logs</t>
+          <t>CMP_business_development_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -25834,7 +21662,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
@@ -25842,7 +21670,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>FUN_business_development_dashboard_controller_audit_logs</t>
+          <t>FUN_business_development_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -25945,7 +21773,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>CMP_cfo_dashboard_controller_audit_logs</t>
+          <t>CMP_cfo_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -25960,7 +21788,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
@@ -25968,7 +21796,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>FUN_cfo_dashboard_controller_audit_logs</t>
+          <t>FUN_cfo_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -26260,7 +22088,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>CMP_chiropractor_dashboard_controller_audit_logs</t>
+          <t>CMP_chiropractor_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -26275,7 +22103,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -26283,7 +22111,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>FUN_chiropractor_dashboard_controller_audit_logs</t>
+          <t>FUN_chiropractor_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -26764,7 +22592,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>CMP_clinic_dashboard_controller_audit_logs</t>
+          <t>CMP_clinic_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -26779,7 +22607,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -26787,7 +22615,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>FUN_clinic_dashboard_controller_audit_logs</t>
+          <t>FUN_clinic_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -27079,7 +22907,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>CMP_clinical_dashboard_controller_audit_logs</t>
+          <t>CMP_clinical_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -27094,7 +22922,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
@@ -27102,7 +22930,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>FUN_clinical_dashboard_controller_audit_logs</t>
+          <t>FUN_clinical_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -27394,7 +23222,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>CMP_community_outreach_dashboard_controller_audit_logs</t>
+          <t>CMP_community_outreach_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -27409,7 +23237,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -27417,7 +23245,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>FUN_community_outreach_dashboard_controller_audit_logs</t>
+          <t>FUN_community_outreach_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -27709,7 +23537,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CMP_compliance_manager_dashboard_controller_audit_logs</t>
+          <t>CMP_compliance_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -27724,7 +23552,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
@@ -27732,7 +23560,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>FUN_compliance_manager_dashboard_controller_audit_logs</t>
+          <t>FUN_compliance_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -27835,7 +23663,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>CMP_coo_dashboard_notifier_audit_logs</t>
+          <t>CMP_coo_dashboard_notifier_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -27850,7 +23678,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H44" s="4" t="n">
@@ -27858,7 +23686,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>FUN_coo_dashboard_notifier_audit_logs</t>
+          <t>FUN_coo_dashboard_notifier_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -27878,7 +23706,7 @@
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>active</t>
         </is>
       </c>
     </row>
@@ -28150,7 +23978,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>CMP_course_architect_dashboard_controller_audit_logs</t>
+          <t>CMP_course_architect_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -28165,7 +23993,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -28173,7 +24001,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>FUN_course_architect_dashboard_controller_audit_logs</t>
+          <t>FUN_course_architect_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -28465,7 +24293,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>CMP_cto_dashboard_controller_audit_logs</t>
+          <t>CMP_cto_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -28480,7 +24308,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H54" s="4" t="n">
@@ -28488,7 +24316,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>FUN_cto_dashboard_controller_audit_logs</t>
+          <t>FUN_cto_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -28780,7 +24608,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>CMP_customer_support_dashboard_controller_audit_logs</t>
+          <t>CMP_customer_support_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -28795,7 +24623,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -28803,7 +24631,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>FUN_customer_support_dashboard_controller_audit_logs</t>
+          <t>FUN_customer_support_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -29095,7 +24923,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>CMP_cx_director_dashboard_controller_audit_logs</t>
+          <t>CMP_cx_director_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -29110,7 +24938,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H64" s="4" t="n">
@@ -29118,7 +24946,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>FUN_cx_director_dashboard_controller_audit_logs</t>
+          <t>FUN_cx_director_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -29410,7 +25238,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>CMP_dynamic_dashboard_controller_audit_logs</t>
+          <t>CMP_dynamic_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -29425,7 +25253,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -29433,7 +25261,7 @@
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>FUN_dynamic_dashboard_controller_audit_logs</t>
+          <t>FUN_dynamic_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -29725,7 +25553,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>CMP_family_member_dashboard_controller_audit_logs</t>
+          <t>CMP_family_member_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -29740,7 +25568,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
@@ -29748,7 +25576,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>FUN_family_member_dashboard_controller_audit_logs</t>
+          <t>FUN_family_member_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -30040,7 +25868,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>CMP_finance_director_dashboard_controller_audit_logs</t>
+          <t>CMP_finance_director_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -30055,7 +25883,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -30063,7 +25891,7 @@
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>FUN_finance_director_dashboard_controller_audit_logs</t>
+          <t>FUN_finance_director_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -30355,7 +26183,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>CMP_franchise_dashboard_controller_audit_logs</t>
+          <t>CMP_franchise_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -30370,7 +26198,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H84" s="4" t="n">
@@ -30378,7 +26206,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>FUN_franchise_dashboard_controller_audit_logs</t>
+          <t>FUN_franchise_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -30670,7 +26498,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>CMP_franchise_sales_manager_dashboard_controller_audit_logs</t>
+          <t>CMP_franchise_sales_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -30685,7 +26513,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -30693,7 +26521,7 @@
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>FUN_franchise_sales_manager_dashboard_controller_audit_logs</t>
+          <t>FUN_franchise_sales_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
@@ -30985,7 +26813,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>CMP_general_manager_dashboard_controller_audit_logs</t>
+          <t>CMP_general_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -31000,7 +26828,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H94" s="4" t="n">
@@ -31008,7 +26836,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>FUN_general_manager_dashboard_controller_audit_logs</t>
+          <t>FUN_general_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -31300,7 +27128,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>CMP_governance_officer_dashboard_controller_audit_logs</t>
+          <t>CMP_governance_officer_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -31315,7 +27143,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -31323,7 +27151,7 @@
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>FUN_governance_officer_dashboard_controller_audit_logs</t>
+          <t>FUN_governance_officer_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
@@ -31615,7 +27443,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>CMP_guest_dashboard_controller_audit_logs</t>
+          <t>CMP_guest_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -31630,7 +27458,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H104" s="4" t="n">
@@ -31638,7 +27466,7 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>FUN_guest_dashboard_controller_audit_logs</t>
+          <t>FUN_guest_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -31930,7 +27758,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>CMP_head_of_bus_dev_dashboard_controller_audit_logs</t>
+          <t>CMP_head_of_bus_dev_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -31945,7 +27773,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -31953,7 +27781,7 @@
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>FUN_head_of_bus_dev_dashboard_controller_audit_logs</t>
+          <t>FUN_head_of_bus_dev_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr">
@@ -32245,7 +28073,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>CMP_head_of_marketing_dashboard_controller_audit_logs</t>
+          <t>CMP_head_of_marketing_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -32260,7 +28088,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H114" s="4" t="n">
@@ -32268,7 +28096,7 @@
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>FUN_head_of_marketing_dashboard_controller_audit_logs</t>
+          <t>FUN_head_of_marketing_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -32560,7 +28388,7 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>CMP_hr_director_dashboard_controller_audit_logs</t>
+          <t>CMP_hr_director_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -32575,7 +28403,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -32583,7 +28411,7 @@
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>FUN_hr_director_dashboard_controller_audit_logs</t>
+          <t>FUN_hr_director_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr">
@@ -32875,7 +28703,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>CMP_hr_hiring_dashboard_controller_audit_logs</t>
+          <t>CMP_hr_hiring_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -32890,7 +28718,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H124" s="4" t="n">
@@ -32898,7 +28726,7 @@
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>FUN_hr_hiring_dashboard_controller_audit_logs</t>
+          <t>FUN_hr_hiring_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
@@ -33190,7 +29018,7 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>CMP_hr_manager_dashboard_controller_audit_logs</t>
+          <t>CMP_hr_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
@@ -33205,7 +29033,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -33213,7 +29041,7 @@
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>FUN_hr_manager_dashboard_controller_audit_logs</t>
+          <t>FUN_hr_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr">
@@ -33505,7 +29333,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>CMP_infrastructure_dashboard_controller_audit_logs</t>
+          <t>CMP_infrastructure_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -33520,7 +29348,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H134" s="4" t="n">
@@ -33528,7 +29356,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>FUN_infrastructure_dashboard_controller_audit_logs</t>
+          <t>FUN_infrastructure_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -33820,7 +29648,7 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>CMP_intake_coordinator_dashboard_controller_audit_logs</t>
+          <t>CMP_intake_coordinator_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
@@ -33835,7 +29663,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -33843,7 +29671,7 @@
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>FUN_intake_coordinator_dashboard_controller_audit_logs</t>
+          <t>FUN_intake_coordinator_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J139" s="3" t="inlineStr">
@@ -34135,7 +29963,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>CMP_intake_dashboard_controller_audit_logs</t>
+          <t>CMP_intake_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -34150,7 +29978,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H144" s="4" t="n">
@@ -34158,7 +29986,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>FUN_intake_dashboard_controller_audit_logs</t>
+          <t>FUN_intake_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -34450,7 +30278,7 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>CMP_legal_dashboard_controller_audit_logs</t>
+          <t>CMP_legal_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -34465,7 +30293,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -34473,7 +30301,7 @@
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>FUN_legal_dashboard_controller_audit_logs</t>
+          <t>FUN_legal_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr">
@@ -34765,7 +30593,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>CMP_local_marketing_manager_dashboard_controller_audit_logs</t>
+          <t>CMP_local_marketing_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -34780,7 +30608,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H154" s="4" t="n">
@@ -34788,7 +30616,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>FUN_local_marketing_manager_dashboard_controller_audit_logs</t>
+          <t>FUN_local_marketing_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -35080,7 +30908,7 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>CMP_office_dashboard_controller_audit_logs</t>
+          <t>CMP_office_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -35095,7 +30923,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -35103,7 +30931,7 @@
       </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>FUN_office_dashboard_controller_audit_logs</t>
+          <t>FUN_office_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J159" s="3" t="inlineStr">
@@ -35395,7 +31223,7 @@
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>CMP_operations_manager_dashboard_controller_audit_logs</t>
+          <t>CMP_operations_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -35410,7 +31238,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H164" s="4" t="n">
@@ -35418,7 +31246,7 @@
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>FUN_operations_manager_dashboard_controller_audit_logs</t>
+          <t>FUN_operations_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
@@ -35710,7 +31538,7 @@
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>CMP_owner_dashboard_controller_audit_logs</t>
+          <t>CMP_owner_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -35725,7 +31553,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -35733,7 +31561,7 @@
       </c>
       <c r="I169" s="3" t="inlineStr">
         <is>
-          <t>FUN_owner_dashboard_controller_audit_logs</t>
+          <t>FUN_owner_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J169" s="3" t="inlineStr">
@@ -36025,7 +31853,7 @@
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>CMP_partnership_manager_dashboard_controller_audit_logs</t>
+          <t>CMP_partnership_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -36040,7 +31868,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H174" s="4" t="n">
@@ -36048,7 +31876,7 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>FUN_partnership_manager_dashboard_controller_audit_logs</t>
+          <t>FUN_partnership_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
@@ -36340,7 +32168,7 @@
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>CMP_patient_dashboard_controller_audit_logs</t>
+          <t>CMP_patient_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
@@ -36355,7 +32183,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -36363,7 +32191,7 @@
       </c>
       <c r="I179" s="3" t="inlineStr">
         <is>
-          <t>FUN_patient_dashboard_controller_audit_logs</t>
+          <t>FUN_patient_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J179" s="3" t="inlineStr">
@@ -36655,7 +32483,7 @@
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>CMP_physiotherapist_dashboard_controller_audit_logs</t>
+          <t>CMP_physiotherapist_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -36670,7 +32498,7 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H184" s="4" t="n">
@@ -36678,7 +32506,7 @@
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>FUN_physiotherapist_dashboard_controller_audit_logs</t>
+          <t>FUN_physiotherapist_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
@@ -36970,7 +32798,7 @@
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>CMP_portal_dashboard_controller_audit_logs</t>
+          <t>CMP_portal_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
@@ -36985,7 +32813,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -36993,7 +32821,7 @@
       </c>
       <c r="I189" s="3" t="inlineStr">
         <is>
-          <t>FUN_portal_dashboard_controller_audit_logs</t>
+          <t>FUN_portal_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J189" s="3" t="inlineStr">
@@ -37285,7 +33113,7 @@
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>CMP_psw_dashboard_controller_audit_logs</t>
+          <t>CMP_psw_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -37300,7 +33128,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H194" s="4" t="n">
@@ -37308,7 +33136,7 @@
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>FUN_psw_dashboard_controller_audit_logs</t>
+          <t>FUN_psw_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
@@ -37600,7 +33428,7 @@
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>CMP_qa_dashboard_controller_audit_logs</t>
+          <t>CMP_qa_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
@@ -37615,7 +33443,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -37623,7 +33451,7 @@
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>FUN_qa_dashboard_controller_audit_logs</t>
+          <t>FUN_qa_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J199" s="3" t="inlineStr">
@@ -37915,7 +33743,7 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>CMP_quality_assurance_dashboard_controller_audit_logs</t>
+          <t>CMP_quality_assurance_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -37930,7 +33758,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H204" s="4" t="n">
@@ -37938,7 +33766,7 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>FUN_quality_assurance_dashboard_controller_audit_logs</t>
+          <t>FUN_quality_assurance_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
@@ -38230,7 +34058,7 @@
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>CMP_receptionist_dashboard_controller_audit_logs</t>
+          <t>CMP_receptionist_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
@@ -38245,7 +34073,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -38253,7 +34081,7 @@
       </c>
       <c r="I209" s="3" t="inlineStr">
         <is>
-          <t>FUN_receptionist_dashboard_controller_audit_logs</t>
+          <t>FUN_receptionist_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J209" s="3" t="inlineStr">
@@ -38545,7 +34373,7 @@
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>CMP_regional_bdm_dashboard_controller_audit_logs</t>
+          <t>CMP_regional_bdm_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -38560,7 +34388,7 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H214" s="4" t="n">
@@ -38568,7 +34396,7 @@
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>FUN_regional_bdm_dashboard_controller_audit_logs</t>
+          <t>FUN_regional_bdm_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
@@ -38860,7 +34688,7 @@
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
-          <t>CMP_regional_manager_usa_dashboard_controller_audit_logs</t>
+          <t>CMP_regional_manager_usa_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
@@ -38875,7 +34703,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -38883,7 +34711,7 @@
       </c>
       <c r="I219" s="3" t="inlineStr">
         <is>
-          <t>FUN_regional_manager_usa_dashboard_controller_audit_logs</t>
+          <t>FUN_regional_manager_usa_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J219" s="3" t="inlineStr">
@@ -39175,7 +35003,7 @@
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>CMP_rmt_dashboard_controller_audit_logs</t>
+          <t>CMP_rmt_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -39190,7 +35018,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H224" s="4" t="n">
@@ -39198,7 +35026,7 @@
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>FUN_rmt_dashboard_controller_audit_logs</t>
+          <t>FUN_rmt_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
@@ -39490,7 +35318,7 @@
       </c>
       <c r="D229" s="3" t="inlineStr">
         <is>
-          <t>CMP_rn_dashboard_controller_audit_logs</t>
+          <t>CMP_rn_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
@@ -39505,7 +35333,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -39513,7 +35341,7 @@
       </c>
       <c r="I229" s="3" t="inlineStr">
         <is>
-          <t>FUN_rn_dashboard_controller_audit_logs</t>
+          <t>FUN_rn_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J229" s="3" t="inlineStr">
@@ -39805,7 +35633,7 @@
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>CMP_rpn_dashboard_controller_audit_logs</t>
+          <t>CMP_rpn_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -39820,7 +35648,7 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H234" s="4" t="n">
@@ -39828,7 +35656,7 @@
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>FUN_rpn_dashboard_controller_audit_logs</t>
+          <t>FUN_rpn_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
@@ -40183,7 +36011,7 @@
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>CMP_scrum_master_dashboard_controller_audit_logs</t>
+          <t>CMP_scrum_master_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -40198,7 +36026,7 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H240" s="4" t="n">
@@ -40206,7 +36034,7 @@
       </c>
       <c r="I240" s="2" t="inlineStr">
         <is>
-          <t>FUN_scrum_master_dashboard_controller_audit_logs</t>
+          <t>FUN_scrum_master_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J240" s="2" t="inlineStr">
@@ -40498,7 +36326,7 @@
       </c>
       <c r="D245" s="3" t="inlineStr">
         <is>
-          <t>CMP_shareholder_dashboard_controller_audit_logs</t>
+          <t>CMP_shareholder_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
@@ -40513,7 +36341,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -40521,7 +36349,7 @@
       </c>
       <c r="I245" s="3" t="inlineStr">
         <is>
-          <t>FUN_shareholder_dashboard_controller_audit_logs</t>
+          <t>FUN_shareholder_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J245" s="3" t="inlineStr">
@@ -40813,7 +36641,7 @@
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>CMP_social_worker_dashboard_controller_audit_logs</t>
+          <t>CMP_social_worker_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -40828,7 +36656,7 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H250" s="4" t="n">
@@ -40836,7 +36664,7 @@
       </c>
       <c r="I250" s="2" t="inlineStr">
         <is>
-          <t>FUN_social_worker_dashboard_controller_audit_logs</t>
+          <t>FUN_social_worker_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J250" s="2" t="inlineStr">
@@ -41128,7 +36956,7 @@
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>CMP_support_dashboard_controller_audit_logs</t>
+          <t>CMP_support_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
@@ -41143,7 +36971,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -41151,7 +36979,7 @@
       </c>
       <c r="I255" s="3" t="inlineStr">
         <is>
-          <t>FUN_support_dashboard_controller_audit_logs</t>
+          <t>FUN_support_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J255" s="3" t="inlineStr">
@@ -41443,7 +37271,7 @@
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>CMP_system_dashboard_controller_audit_logs</t>
+          <t>CMP_system_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -41458,7 +37286,7 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H260" s="4" t="n">
@@ -41466,7 +37294,7 @@
       </c>
       <c r="I260" s="2" t="inlineStr">
         <is>
-          <t>FUN_system_dashboard_controller_audit_logs</t>
+          <t>FUN_system_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J260" s="2" t="inlineStr">
@@ -41758,7 +37586,7 @@
       </c>
       <c r="D265" s="3" t="inlineStr">
         <is>
-          <t>CMP_system_verification_dashboard_controller_audit_logs</t>
+          <t>CMP_system_verification_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
@@ -41773,7 +37601,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -41781,7 +37609,7 @@
       </c>
       <c r="I265" s="3" t="inlineStr">
         <is>
-          <t>FUN_system_verification_dashboard_controller_audit_logs</t>
+          <t>FUN_system_verification_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J265" s="3" t="inlineStr">
@@ -42073,7 +37901,7 @@
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>CMP_territory_expansion_manager_dashboard_controller_audit_logs</t>
+          <t>CMP_territory_expansion_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -42088,7 +37916,7 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H270" s="4" t="n">
@@ -42096,7 +37924,7 @@
       </c>
       <c r="I270" s="2" t="inlineStr">
         <is>
-          <t>FUN_territory_expansion_manager_dashboard_controller_audit_logs</t>
+          <t>FUN_territory_expansion_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J270" s="2" t="inlineStr">
@@ -42388,7 +38216,7 @@
       </c>
       <c r="D275" s="3" t="inlineStr">
         <is>
-          <t>CMP_territory_sales_manager_dashboard_controller_audit_logs</t>
+          <t>CMP_territory_sales_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
@@ -42403,7 +38231,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -42411,7 +38239,7 @@
       </c>
       <c r="I275" s="3" t="inlineStr">
         <is>
-          <t>FUN_territory_sales_manager_dashboard_controller_audit_logs</t>
+          <t>FUN_territory_sales_manager_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J275" s="3" t="inlineStr">
@@ -42703,7 +38531,7 @@
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>CMP_training_coordinator_dashboard_controller_audit_logs</t>
+          <t>CMP_training_coordinator_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -42718,7 +38546,7 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H280" s="4" t="n">
@@ -42726,7 +38554,7 @@
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>FUN_training_coordinator_dashboard_controller_audit_logs</t>
+          <t>FUN_training_coordinator_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
@@ -43018,7 +38846,7 @@
       </c>
       <c r="D285" s="3" t="inlineStr">
         <is>
-          <t>CMP_training_director_dashboard_controller_audit_logs</t>
+          <t>CMP_training_director_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E285" s="3" t="inlineStr">
@@ -43033,7 +38861,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -43041,7 +38869,7 @@
       </c>
       <c r="I285" s="3" t="inlineStr">
         <is>
-          <t>FUN_training_director_dashboard_controller_audit_logs</t>
+          <t>FUN_training_director_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J285" s="3" t="inlineStr">
@@ -43333,7 +39161,7 @@
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>CMP_training_hub_dashboard_controller_audit_logs</t>
+          <t>CMP_training_hub_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -43348,7 +39176,7 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H290" s="4" t="n">
@@ -43356,7 +39184,7 @@
       </c>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>FUN_training_hub_dashboard_controller_audit_logs</t>
+          <t>FUN_training_hub_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J290" s="2" t="inlineStr">
@@ -43648,7 +39476,7 @@
       </c>
       <c r="D295" s="3" t="inlineStr">
         <is>
-          <t>CMP_volunteer_coordinator_dashboard_controller_audit_logs</t>
+          <t>CMP_volunteer_coordinator_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="E295" s="3" t="inlineStr">
@@ -43663,7 +39491,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>data-cy-audit-logs</t>
+          <t>data-cy-audit-logs-terminal</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -43671,7 +39499,7 @@
       </c>
       <c r="I295" s="3" t="inlineStr">
         <is>
-          <t>FUN_volunteer_coordinator_dashboard_controller_audit_logs</t>
+          <t>FUN_volunteer_coordinator_dashboard_controller_audit_logs_terminal</t>
         </is>
       </c>
       <c r="J295" s="3" t="inlineStr">
@@ -43812,12 +39640,12 @@
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
@@ -43860,12 +39688,12 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
@@ -43908,12 +39736,12 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
@@ -44050,7 +39878,7 @@
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
@@ -44103,7 +39931,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
@@ -44156,7 +39984,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2026-05-21 21:52:37</t>
+          <t>2026-05-22 15:02:56</t>
         </is>
       </c>
     </row>
